--- a/output/pdf_financials_xlsx/MKR.xlsx
+++ b/output/pdf_financials_xlsx/MKR.xlsx
@@ -5999,16 +5999,16 @@
         <v>5.655638</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.798838</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.818009</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.825857</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>5.943798</v>
       </c>
     </row>
     <row r="93">
@@ -7423,49 +7423,49 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.48665</v>
+        <v>-2.592773</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.856638</v>
+        <v>-0.789802</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.967449</v>
+        <v>0.369981</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>3.480205</v>
+        <v>3.28475</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.258502</v>
+        <v>-0.011078</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.152988</v>
+        <v>-0.262567</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.03748</v>
+        <v>-0.41833</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.962481</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.73694</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.646563</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.765783</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.145</v>
+        <v>-0.16363</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.171966</v>
+        <v>-1.201664</v>
       </c>
       <c r="Q118" s="3" t="n">
         <v>0.0475</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>0.13125</v>
       </c>
     </row>
     <row r="119">
@@ -9379,7 +9379,11 @@
           <t>Reserves (note 5)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -10355,7 +10359,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -17942,7 +17950,11 @@
           <t>Common shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -19432,7 +19444,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -20681,7 +20697,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -23800,7 +23820,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -26039,7 +26063,11 @@
           <t>Exploration and evaluation expenses</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MKR.xlsx
+++ b/output/pdf_financials_xlsx/MKR.xlsx
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.061685</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.030667</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.044034</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0.011506</v>
@@ -1063,25 +1063,25 @@
         <v>8.000000000000001e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.00726</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.002473</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.005525</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.020553</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.090379</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.114022</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.066704</v>
       </c>
     </row>
     <row r="13">
@@ -2041,13 +2041,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.30985</v>
+        <v>-6.371535</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.014034</v>
+        <v>-1.044701</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.293401</v>
+        <v>-1.337435</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.586438</v>
@@ -2071,25 +2071,25 @@
         <v>0.408567</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.014399</v>
+        <v>0.007139</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.636361</v>
+        <v>-0.638834</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.024799</v>
+        <v>0.019274</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.331301</v>
+        <v>-0.351854</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.150072</v>
+        <v>-0.240451</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.520685</v>
+        <v>-0.634707</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.513199</v>
+        <v>-1.579903</v>
       </c>
     </row>
     <row r="28">
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.30985</v>
+        <v>-6.371535</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.014034</v>
+        <v>-1.044701</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.293401</v>
+        <v>-1.337435</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.586438</v>
@@ -2187,25 +2187,25 @@
         <v>0.408567</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.014399</v>
+        <v>0.007139</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.636361</v>
+        <v>-0.638834</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.024799</v>
+        <v>0.019274</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.331301</v>
+        <v>-0.351854</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.150072</v>
+        <v>-0.240451</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.520685</v>
+        <v>-0.634707</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.513199</v>
+        <v>-1.579903</v>
       </c>
     </row>
     <row r="30">
@@ -2464,19 +2464,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.585654</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.117421</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.050092</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.023495</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.437185</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.254579</v>
@@ -2488,31 +2488,31 @@
         <v>0.154225</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.156477</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.241166</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.02341</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.523862</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.032383</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.429055</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>2.252578</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.991833</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.095001</v>
       </c>
     </row>
     <row r="35">
@@ -2580,19 +2580,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>2.781533</v>
+        <v>3.367187</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>5.69533</v>
+        <v>5.812751</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.226396</v>
+        <v>2.276488</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.27937</v>
+        <v>1.302865</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.437185</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.254579</v>
@@ -2604,31 +2604,31 @@
         <v>0.689463</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.66207</v>
+        <v>0.818547</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.569563</v>
+        <v>1.810729</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.49</v>
+        <v>1.51341</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.34</v>
+        <v>0.863862</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.215001</v>
+        <v>2.247384</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.257001</v>
+        <v>2.686056</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>2.252578</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.991833</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>2.095001</v>
       </c>
     </row>
     <row r="37">
@@ -3276,19 +3276,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.8468560000000001</v>
+        <v>0.261202</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.394596</v>
+        <v>0.277175</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.280787</v>
+        <v>0.230695</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.359225</v>
+        <v>0.33573</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.637849</v>
+        <v>0.200664</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.204182</v>
@@ -3300,28 +3300,28 @@
         <v>0.006097</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.161202</v>
+        <v>0.004725</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.279033</v>
+        <v>0.037867</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.03196</v>
+        <v>0.00855</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.536862</v>
+        <v>0.013</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.048156</v>
+        <v>0.015773</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.451885</v>
+        <v>0.02283</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.277218</v>
+        <v>0.02464</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.018292</v>
+        <v>0.026459</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -32334,7 +32334,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -46157,7 +46157,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E389" s="5" t="n">

--- a/output/pdf_financials_xlsx/MKR.xlsx
+++ b/output/pdf_financials_xlsx/MKR.xlsx
@@ -749,13 +749,13 @@
         <v>0.229929</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.213341</v>
+        <v>0.325747</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.203843</v>
+        <v>0.315361</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.172997</v>
+        <v>0.271676</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.08577600000000001</v>
@@ -1338,7 +1338,7 @@
         <v>0.051209</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.0197</v>
+        <v>-0.0197</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -7212,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="L114" s="3" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-0.215001</v>
       </c>
       <c r="O114" s="3" t="n">
         <v>0</v>
@@ -7267,25 +7267,25 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.396498</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.050122</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.274184</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.152961</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>1.082878</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.03334</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -18407,7 +18407,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -19642,7 +19646,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -20994,7 +21002,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -22499,7 +22511,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -24026,7 +24042,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -26354,7 +26374,11 @@
           <t>Issuance of common shares in private placement</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -26938,7 +26962,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -27233,7 +27261,11 @@
           <t>Deferred income taxes recovery</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -27726,7 +27758,11 @@
           <t>Issuance of common shares by flow through private placement</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -30639,7 +30675,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -42692,7 +42732,11 @@
           <t>Deferred income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -44688,7 +44732,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
